--- a/src/main/resources/other/总结.xlsx
+++ b/src/main/resources/other/总结.xlsx
@@ -4,19 +4,22 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28245" windowHeight="12465" activeTab="2"/>
+    <workbookView windowWidth="28245" windowHeight="12465" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="数据表" sheetId="5" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="前端调后台" sheetId="6" r:id="rId4"/>
+    <sheet name="后台返回数据处理" sheetId="7" r:id="rId5"/>
+    <sheet name="前转后的数据" sheetId="8" r:id="rId6"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1134" uniqueCount="315">
   <si>
     <t>场景</t>
   </si>
@@ -775,6 +778,192 @@
   </si>
   <si>
     <t>元素事件绑定信息</t>
+  </si>
+  <si>
+    <t>元素类型</t>
+  </si>
+  <si>
+    <t>触发事件</t>
+  </si>
+  <si>
+    <t>目的</t>
+  </si>
+  <si>
+    <t>请求参数</t>
+  </si>
+  <si>
+    <t>调后台成功后</t>
+  </si>
+  <si>
+    <t>点击</t>
+  </si>
+  <si>
+    <t>获取菜单初始页元素信息</t>
+  </si>
+  <si>
+    <t>菜单码+页码+事件元素名+事件类型+页面所有元素数据</t>
+  </si>
+  <si>
+    <t>刷新页面</t>
+  </si>
+  <si>
+    <t>查询“菜单码+页码+事件元素名+事件类型”对应事件响应配置记录，按配置执行对应逻辑</t>
+  </si>
+  <si>
+    <t>按钮_弹窗子页</t>
+  </si>
+  <si>
+    <t>获取弹窗子页初始元素信息</t>
+  </si>
+  <si>
+    <t>刷新页面_弹窗子页</t>
+  </si>
+  <si>
+    <t>按钮_后台处理</t>
+  </si>
+  <si>
+    <t>触发后台处理增删改查</t>
+  </si>
+  <si>
+    <t>输入类元素</t>
+  </si>
+  <si>
+    <t>变更</t>
+  </si>
+  <si>
+    <t>获取关联元素初始数据</t>
+  </si>
+  <si>
+    <t>刷新页面_改变关联元素初始数据</t>
+  </si>
+  <si>
+    <t>父级元素</t>
+  </si>
+  <si>
+    <t>数据类型</t>
+  </si>
+  <si>
+    <t>对象</t>
+  </si>
+  <si>
+    <t>页面元素定位</t>
+  </si>
+  <si>
+    <t>变更数据</t>
+  </si>
+  <si>
+    <t>div</t>
+  </si>
+  <si>
+    <t>parentEleId</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>attr</t>
+  </si>
+  <si>
+    <t>调接口</t>
+  </si>
+  <si>
+    <t>menugroup</t>
+  </si>
+  <si>
+    <t>class="menuDropDown"</t>
+  </si>
+  <si>
+    <t>关闭弹窗</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>menuGroupName</t>
+  </si>
+  <si>
+    <t>class="menuDropButton"</t>
+  </si>
+  <si>
+    <t>class="menuDropDown-content"</t>
+  </si>
+  <si>
+    <t>menuName</t>
+  </si>
+  <si>
+    <t>event</t>
+  </si>
+  <si>
+    <t>class="inputArea_div_grp",attr</t>
+  </si>
+  <si>
+    <t>label</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>class="inputArea_sub_label"</t>
+  </si>
+  <si>
+    <t>defaultValue</t>
+  </si>
+  <si>
+    <t>class="inputArea_sub_input"</t>
+  </si>
+  <si>
+    <t>提示语</t>
+  </si>
+  <si>
+    <t>class="inputArea_sub_input",type="file",multiple=null</t>
+  </si>
+  <si>
+    <t>InputDataList</t>
+  </si>
+  <si>
+    <t>class="inputArea_sub_input",list=dataList+id</t>
+  </si>
+  <si>
+    <t>datalist</t>
+  </si>
+  <si>
+    <t>dataList+id</t>
+  </si>
+  <si>
+    <t>option</t>
+  </si>
+  <si>
+    <t>key,value</t>
+  </si>
+  <si>
+    <t>...</t>
+  </si>
+  <si>
+    <t>MultipleSelect</t>
+  </si>
+  <si>
+    <t>multiple="multiple"</t>
+  </si>
+  <si>
+    <t>data</t>
+  </si>
+  <si>
+    <t>SelectOption</t>
+  </si>
+  <si>
+    <t>Button</t>
+  </si>
+  <si>
+    <t>span</t>
+  </si>
+  <si>
+    <t>事件对象的数据</t>
+  </si>
+  <si>
+    <t>事件对象为表格记录时，需要读取本条记录数据</t>
+  </si>
+  <si>
+    <t>页面输入字段的数据</t>
   </si>
 </sst>
 </file>
@@ -787,7 +976,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -804,14 +993,76 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="10.5"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -831,14 +1082,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
@@ -846,25 +1089,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -876,17 +1105,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -900,6 +1120,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
@@ -908,32 +1135,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -942,13 +1145,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -963,7 +1159,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -981,7 +1213,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -993,31 +1237,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1035,7 +1261,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1047,49 +1321,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1099,61 +1343,37 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1172,11 +1392,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1192,6 +1418,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1220,30 +1455,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -1262,10 +1473,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1274,138 +1485,150 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1423,7 +1646,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3269,16 +3492,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>657225</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>115570</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>154940</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>544195</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>2540</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -3287,7 +3510,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4371975" y="514350"/>
+          <a:off x="4114800" y="533400"/>
           <a:ext cx="1944370" cy="1526540"/>
           <a:chOff x="7890" y="270"/>
           <a:chExt cx="3062" cy="2404"/>
@@ -7172,7 +7395,7 @@
       <c r="A7" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C7" t="s">
@@ -7180,13 +7403,13 @@
       </c>
     </row>
     <row r="8" spans="2:4">
-      <c r="B8" s="2"/>
+      <c r="B8" s="6"/>
       <c r="D8" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="9" spans="2:12">
-      <c r="B9" s="2"/>
+      <c r="B9" s="6"/>
       <c r="D9" t="s">
         <v>20</v>
       </c>
@@ -7198,15 +7421,15 @@
       </c>
     </row>
     <row r="10" spans="2:20">
-      <c r="B10" s="2"/>
+      <c r="B10" s="6"/>
       <c r="D10" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
       <c r="K10" t="s">
         <v>23</v>
       </c>
@@ -7219,458 +7442,458 @@
       <c r="N10" t="s">
         <v>26</v>
       </c>
-      <c r="O10" s="3"/>
-      <c r="P10" s="3"/>
-      <c r="Q10" s="3"/>
-      <c r="R10" s="3"/>
-      <c r="S10" s="3"/>
-      <c r="T10" s="3"/>
+      <c r="O10" s="7"/>
+      <c r="P10" s="7"/>
+      <c r="Q10" s="7"/>
+      <c r="R10" s="7"/>
+      <c r="S10" s="7"/>
+      <c r="T10" s="7"/>
     </row>
     <row r="11" spans="4:20">
       <c r="D11" t="s">
         <v>27</v>
       </c>
-      <c r="F11" s="3"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4"/>
-      <c r="M11" s="4"/>
-      <c r="N11" s="4"/>
-      <c r="O11" s="4"/>
-      <c r="P11" s="4"/>
-      <c r="Q11" s="4"/>
-      <c r="R11" s="4"/>
-      <c r="S11" s="4"/>
-      <c r="T11" s="4"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="8"/>
+      <c r="P11" s="8"/>
+      <c r="Q11" s="8"/>
+      <c r="R11" s="8"/>
+      <c r="S11" s="8"/>
+      <c r="T11" s="8"/>
     </row>
     <row r="12" spans="6:20">
-      <c r="F12" s="3"/>
-      <c r="G12" s="5" t="s">
+      <c r="F12" s="7"/>
+      <c r="G12" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="5"/>
-      <c r="N12" s="5"/>
-      <c r="O12" s="5"/>
-      <c r="P12" s="5"/>
-      <c r="Q12" s="5"/>
-      <c r="R12" s="5"/>
-      <c r="S12" s="5"/>
-      <c r="T12" s="5"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="9"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="9"/>
+      <c r="O12" s="9"/>
+      <c r="P12" s="9"/>
+      <c r="Q12" s="9"/>
+      <c r="R12" s="9"/>
+      <c r="S12" s="9"/>
+      <c r="T12" s="9"/>
     </row>
     <row r="13" spans="2:20">
-      <c r="B13" s="2"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3">
+      <c r="B13" s="6"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7">
         <v>1</v>
       </c>
-      <c r="H13" s="3" t="s">
+      <c r="H13" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="3"/>
-      <c r="P13" s="3"/>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="3"/>
-      <c r="S13" s="3"/>
-      <c r="T13" s="3"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
+      <c r="O13" s="7"/>
+      <c r="P13" s="7"/>
+      <c r="Q13" s="7"/>
+      <c r="R13" s="7"/>
+      <c r="S13" s="7"/>
+      <c r="T13" s="7"/>
     </row>
     <row r="14" spans="2:20">
-      <c r="B14" s="2"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3">
+      <c r="B14" s="6"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7">
         <v>2</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="H14" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="3"/>
-      <c r="P14" s="3"/>
-      <c r="Q14" s="3"/>
-      <c r="R14" s="3"/>
-      <c r="S14" s="3"/>
-      <c r="T14" s="3"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="7"/>
+      <c r="O14" s="7"/>
+      <c r="P14" s="7"/>
+      <c r="Q14" s="7"/>
+      <c r="R14" s="7"/>
+      <c r="S14" s="7"/>
+      <c r="T14" s="7"/>
     </row>
     <row r="15" spans="6:20">
-      <c r="F15" s="3"/>
-      <c r="G15" s="3">
+      <c r="F15" s="7"/>
+      <c r="G15" s="7">
         <v>3</v>
       </c>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="3"/>
-      <c r="P15" s="3"/>
-      <c r="Q15" s="3"/>
-      <c r="R15" s="3"/>
-      <c r="S15" s="3"/>
-      <c r="T15" s="3"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="7"/>
+      <c r="O15" s="7"/>
+      <c r="P15" s="7"/>
+      <c r="Q15" s="7"/>
+      <c r="R15" s="7"/>
+      <c r="S15" s="7"/>
+      <c r="T15" s="7"/>
     </row>
     <row r="16" spans="6:20">
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
-      <c r="N16" s="3"/>
-      <c r="O16" s="3"/>
-      <c r="P16" s="3"/>
-      <c r="Q16" s="3"/>
-      <c r="R16" s="3"/>
-      <c r="S16" s="3"/>
-      <c r="T16" s="3"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="7"/>
+      <c r="N16" s="7"/>
+      <c r="O16" s="7"/>
+      <c r="P16" s="7"/>
+      <c r="Q16" s="7"/>
+      <c r="R16" s="7"/>
+      <c r="S16" s="7"/>
+      <c r="T16" s="7"/>
     </row>
     <row r="17" spans="2:20">
-      <c r="B17" s="2"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
-      <c r="N17" s="3"/>
-      <c r="O17" s="3"/>
-      <c r="P17" s="3"/>
-      <c r="Q17" s="3"/>
-      <c r="R17" s="3"/>
-      <c r="S17" s="3"/>
-      <c r="T17" s="3"/>
+      <c r="B17" s="6"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="7"/>
+      <c r="O17" s="7"/>
+      <c r="P17" s="7"/>
+      <c r="Q17" s="7"/>
+      <c r="R17" s="7"/>
+      <c r="S17" s="7"/>
+      <c r="T17" s="7"/>
     </row>
     <row r="18" spans="2:20">
-      <c r="B18" s="2"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
-      <c r="N18" s="3"/>
-      <c r="O18" s="3"/>
-      <c r="P18" s="3"/>
-      <c r="Q18" s="3"/>
-      <c r="R18" s="3"/>
-      <c r="S18" s="3"/>
-      <c r="T18" s="3"/>
+      <c r="B18" s="6"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="7"/>
+      <c r="M18" s="7"/>
+      <c r="N18" s="7"/>
+      <c r="O18" s="7"/>
+      <c r="P18" s="7"/>
+      <c r="Q18" s="7"/>
+      <c r="R18" s="7"/>
+      <c r="S18" s="7"/>
+      <c r="T18" s="7"/>
     </row>
     <row r="19" spans="6:20">
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
-      <c r="M19" s="3"/>
-      <c r="N19" s="3"/>
-      <c r="O19" s="3"/>
-      <c r="P19" s="3"/>
-      <c r="Q19" s="3"/>
-      <c r="R19" s="3"/>
-      <c r="S19" s="3"/>
-      <c r="T19" s="3"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="7"/>
+      <c r="M19" s="7"/>
+      <c r="N19" s="7"/>
+      <c r="O19" s="7"/>
+      <c r="P19" s="7"/>
+      <c r="Q19" s="7"/>
+      <c r="R19" s="7"/>
+      <c r="S19" s="7"/>
+      <c r="T19" s="7"/>
     </row>
     <row r="20" spans="6:20">
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3"/>
-      <c r="M20" s="3"/>
-      <c r="N20" s="3"/>
-      <c r="O20" s="3"/>
-      <c r="P20" s="3"/>
-      <c r="Q20" s="3"/>
-      <c r="R20" s="3"/>
-      <c r="S20" s="3"/>
-      <c r="T20" s="3"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="7"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="7"/>
+      <c r="M20" s="7"/>
+      <c r="N20" s="7"/>
+      <c r="O20" s="7"/>
+      <c r="P20" s="7"/>
+      <c r="Q20" s="7"/>
+      <c r="R20" s="7"/>
+      <c r="S20" s="7"/>
+      <c r="T20" s="7"/>
     </row>
     <row r="21" spans="2:20">
-      <c r="B21" s="2"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
-      <c r="L21" s="3"/>
-      <c r="M21" s="3"/>
-      <c r="N21" s="3"/>
-      <c r="O21" s="3"/>
-      <c r="P21" s="3"/>
-      <c r="Q21" s="3"/>
-      <c r="R21" s="3"/>
-      <c r="S21" s="3"/>
-      <c r="T21" s="3"/>
+      <c r="B21" s="6"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="7"/>
+      <c r="M21" s="7"/>
+      <c r="N21" s="7"/>
+      <c r="O21" s="7"/>
+      <c r="P21" s="7"/>
+      <c r="Q21" s="7"/>
+      <c r="R21" s="7"/>
+      <c r="S21" s="7"/>
+      <c r="T21" s="7"/>
     </row>
     <row r="22" spans="2:20">
-      <c r="B22" s="2"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
-      <c r="M22" s="3"/>
-      <c r="N22" s="3"/>
-      <c r="O22" s="3"/>
-      <c r="P22" s="3"/>
-      <c r="Q22" s="3"/>
-      <c r="R22" s="3"/>
-      <c r="S22" s="3"/>
-      <c r="T22" s="3"/>
+      <c r="B22" s="6"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="7"/>
+      <c r="L22" s="7"/>
+      <c r="M22" s="7"/>
+      <c r="N22" s="7"/>
+      <c r="O22" s="7"/>
+      <c r="P22" s="7"/>
+      <c r="Q22" s="7"/>
+      <c r="R22" s="7"/>
+      <c r="S22" s="7"/>
+      <c r="T22" s="7"/>
     </row>
     <row r="23" spans="6:20">
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
-      <c r="M23" s="3"/>
-      <c r="N23" s="3"/>
-      <c r="O23" s="3"/>
-      <c r="P23" s="3"/>
-      <c r="Q23" s="3"/>
-      <c r="R23" s="3"/>
-      <c r="S23" s="3"/>
-      <c r="T23" s="6"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="7"/>
+      <c r="J23" s="7"/>
+      <c r="K23" s="7"/>
+      <c r="L23" s="7"/>
+      <c r="M23" s="7"/>
+      <c r="N23" s="7"/>
+      <c r="O23" s="7"/>
+      <c r="P23" s="7"/>
+      <c r="Q23" s="7"/>
+      <c r="R23" s="7"/>
+      <c r="S23" s="7"/>
+      <c r="T23" s="10"/>
     </row>
     <row r="24" spans="6:20">
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
-      <c r="M24" s="3"/>
-      <c r="N24" s="3"/>
-      <c r="O24" s="3"/>
-      <c r="P24" s="3"/>
-      <c r="Q24" s="3"/>
-      <c r="R24" s="3"/>
-      <c r="S24" s="3"/>
-      <c r="T24" s="3"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
+      <c r="I24" s="7"/>
+      <c r="J24" s="7"/>
+      <c r="K24" s="7"/>
+      <c r="L24" s="7"/>
+      <c r="M24" s="7"/>
+      <c r="N24" s="7"/>
+      <c r="O24" s="7"/>
+      <c r="P24" s="7"/>
+      <c r="Q24" s="7"/>
+      <c r="R24" s="7"/>
+      <c r="S24" s="7"/>
+      <c r="T24" s="7"/>
     </row>
     <row r="25" spans="6:20">
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
-      <c r="N25" s="3"/>
-      <c r="O25" s="3"/>
-      <c r="P25" s="3"/>
-      <c r="Q25" s="3"/>
-      <c r="R25" s="3"/>
-      <c r="S25" s="3"/>
-      <c r="T25" s="3"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7"/>
+      <c r="K25" s="7"/>
+      <c r="L25" s="7"/>
+      <c r="M25" s="7"/>
+      <c r="N25" s="7"/>
+      <c r="O25" s="7"/>
+      <c r="P25" s="7"/>
+      <c r="Q25" s="7"/>
+      <c r="R25" s="7"/>
+      <c r="S25" s="7"/>
+      <c r="T25" s="7"/>
     </row>
     <row r="26" spans="6:20">
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
-      <c r="M26" s="3"/>
-      <c r="N26" s="3"/>
-      <c r="O26" s="3"/>
-      <c r="P26" s="3"/>
-      <c r="Q26" s="3"/>
-      <c r="R26" s="3"/>
-      <c r="S26" s="3"/>
-      <c r="T26" s="3"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="7"/>
+      <c r="J26" s="7"/>
+      <c r="K26" s="7"/>
+      <c r="L26" s="7"/>
+      <c r="M26" s="7"/>
+      <c r="N26" s="7"/>
+      <c r="O26" s="7"/>
+      <c r="P26" s="7"/>
+      <c r="Q26" s="7"/>
+      <c r="R26" s="7"/>
+      <c r="S26" s="7"/>
+      <c r="T26" s="7"/>
     </row>
     <row r="27" spans="6:20">
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
-      <c r="M27" s="3"/>
-      <c r="N27" s="3"/>
-      <c r="O27" s="3"/>
-      <c r="P27" s="3"/>
-      <c r="Q27" s="3"/>
-      <c r="R27" s="3"/>
-      <c r="S27" s="3"/>
-      <c r="T27" s="3"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="7"/>
+      <c r="I27" s="7"/>
+      <c r="J27" s="7"/>
+      <c r="K27" s="7"/>
+      <c r="L27" s="7"/>
+      <c r="M27" s="7"/>
+      <c r="N27" s="7"/>
+      <c r="O27" s="7"/>
+      <c r="P27" s="7"/>
+      <c r="Q27" s="7"/>
+      <c r="R27" s="7"/>
+      <c r="S27" s="7"/>
+      <c r="T27" s="7"/>
     </row>
     <row r="28" spans="6:20">
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
-      <c r="J28" s="3"/>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
-      <c r="M28" s="3"/>
-      <c r="N28" s="3"/>
-      <c r="O28" s="3"/>
-      <c r="P28" s="3"/>
-      <c r="Q28" s="3"/>
-      <c r="R28" s="3"/>
-      <c r="S28" s="3"/>
-      <c r="T28" s="3"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="7"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="7"/>
+      <c r="L28" s="7"/>
+      <c r="M28" s="7"/>
+      <c r="N28" s="7"/>
+      <c r="O28" s="7"/>
+      <c r="P28" s="7"/>
+      <c r="Q28" s="7"/>
+      <c r="R28" s="7"/>
+      <c r="S28" s="7"/>
+      <c r="T28" s="7"/>
     </row>
     <row r="29" spans="6:20">
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
-      <c r="J29" s="3"/>
-      <c r="K29" s="3"/>
-      <c r="L29" s="3"/>
-      <c r="M29" s="3"/>
-      <c r="N29" s="3"/>
-      <c r="O29" s="3"/>
-      <c r="P29" s="3"/>
-      <c r="Q29" s="3"/>
-      <c r="R29" s="3"/>
-      <c r="S29" s="3"/>
-      <c r="T29" s="3"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="7"/>
+      <c r="J29" s="7"/>
+      <c r="K29" s="7"/>
+      <c r="L29" s="7"/>
+      <c r="M29" s="7"/>
+      <c r="N29" s="7"/>
+      <c r="O29" s="7"/>
+      <c r="P29" s="7"/>
+      <c r="Q29" s="7"/>
+      <c r="R29" s="7"/>
+      <c r="S29" s="7"/>
+      <c r="T29" s="7"/>
     </row>
     <row r="30" spans="6:20">
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
-      <c r="J30" s="3"/>
-      <c r="K30" s="3"/>
-      <c r="L30" s="3"/>
-      <c r="M30" s="3"/>
-      <c r="N30" s="3"/>
-      <c r="O30" s="3"/>
-      <c r="P30" s="3"/>
-      <c r="Q30" s="3"/>
-      <c r="R30" s="3"/>
-      <c r="S30" s="3"/>
-      <c r="T30" s="3"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="7"/>
+      <c r="H30" s="7"/>
+      <c r="I30" s="7"/>
+      <c r="J30" s="7"/>
+      <c r="K30" s="7"/>
+      <c r="L30" s="7"/>
+      <c r="M30" s="7"/>
+      <c r="N30" s="7"/>
+      <c r="O30" s="7"/>
+      <c r="P30" s="7"/>
+      <c r="Q30" s="7"/>
+      <c r="R30" s="7"/>
+      <c r="S30" s="7"/>
+      <c r="T30" s="7"/>
     </row>
     <row r="31" spans="6:20">
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
-      <c r="J31" s="3"/>
-      <c r="K31" s="3"/>
-      <c r="L31" s="3"/>
-      <c r="M31" s="3"/>
-      <c r="N31" s="3"/>
-      <c r="O31" s="3"/>
-      <c r="P31" s="3"/>
-      <c r="Q31" s="3"/>
-      <c r="R31" s="3"/>
-      <c r="S31" s="3"/>
-      <c r="T31" s="3"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7"/>
+      <c r="H31" s="7"/>
+      <c r="I31" s="7"/>
+      <c r="J31" s="7"/>
+      <c r="K31" s="7"/>
+      <c r="L31" s="7"/>
+      <c r="M31" s="7"/>
+      <c r="N31" s="7"/>
+      <c r="O31" s="7"/>
+      <c r="P31" s="7"/>
+      <c r="Q31" s="7"/>
+      <c r="R31" s="7"/>
+      <c r="S31" s="7"/>
+      <c r="T31" s="7"/>
     </row>
     <row r="32" spans="6:20">
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
-      <c r="J32" s="3"/>
-      <c r="K32" s="3"/>
-      <c r="L32" s="3"/>
-      <c r="M32" s="3"/>
-      <c r="N32" s="3"/>
-      <c r="O32" s="3"/>
-      <c r="P32" s="3"/>
-      <c r="Q32" s="3"/>
-      <c r="R32" s="3"/>
-      <c r="S32" s="3"/>
-      <c r="T32" s="3"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="7"/>
+      <c r="H32" s="7"/>
+      <c r="I32" s="7"/>
+      <c r="J32" s="7"/>
+      <c r="K32" s="7"/>
+      <c r="L32" s="7"/>
+      <c r="M32" s="7"/>
+      <c r="N32" s="7"/>
+      <c r="O32" s="7"/>
+      <c r="P32" s="7"/>
+      <c r="Q32" s="7"/>
+      <c r="R32" s="7"/>
+      <c r="S32" s="7"/>
+      <c r="T32" s="7"/>
     </row>
     <row r="33" spans="6:20">
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
-      <c r="J33" s="3"/>
-      <c r="K33" s="3"/>
-      <c r="L33" s="3"/>
-      <c r="M33" s="3"/>
-      <c r="N33" s="3"/>
-      <c r="O33" s="3"/>
-      <c r="P33" s="3"/>
-      <c r="Q33" s="3"/>
-      <c r="R33" s="3"/>
-      <c r="S33" s="3"/>
-      <c r="T33" s="3"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="7"/>
+      <c r="H33" s="7"/>
+      <c r="I33" s="7"/>
+      <c r="J33" s="7"/>
+      <c r="K33" s="7"/>
+      <c r="L33" s="7"/>
+      <c r="M33" s="7"/>
+      <c r="N33" s="7"/>
+      <c r="O33" s="7"/>
+      <c r="P33" s="7"/>
+      <c r="Q33" s="7"/>
+      <c r="R33" s="7"/>
+      <c r="S33" s="7"/>
+      <c r="T33" s="7"/>
     </row>
     <row r="34" spans="6:20">
-      <c r="F34" s="3"/>
-      <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
-      <c r="J34" s="3"/>
-      <c r="K34" s="3"/>
-      <c r="L34" s="3"/>
-      <c r="M34" s="3"/>
-      <c r="N34" s="3"/>
-      <c r="O34" s="3"/>
-      <c r="P34" s="3"/>
-      <c r="Q34" s="3"/>
-      <c r="R34" s="3"/>
-      <c r="S34" s="3"/>
-      <c r="T34" s="3"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="7"/>
+      <c r="H34" s="7"/>
+      <c r="I34" s="7"/>
+      <c r="J34" s="7"/>
+      <c r="K34" s="7"/>
+      <c r="L34" s="7"/>
+      <c r="M34" s="7"/>
+      <c r="N34" s="7"/>
+      <c r="O34" s="7"/>
+      <c r="P34" s="7"/>
+      <c r="Q34" s="7"/>
+      <c r="R34" s="7"/>
+      <c r="S34" s="7"/>
+      <c r="T34" s="7"/>
     </row>
     <row r="35" spans="6:20">
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
-      <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
-      <c r="J35" s="3"/>
-      <c r="K35" s="3"/>
-      <c r="L35" s="3"/>
-      <c r="M35" s="3"/>
-      <c r="N35" s="3"/>
-      <c r="O35" s="3"/>
-      <c r="P35" s="3"/>
-      <c r="Q35" s="3"/>
-      <c r="R35" s="3"/>
-      <c r="S35" s="3"/>
-      <c r="T35" s="3"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="7"/>
+      <c r="H35" s="7"/>
+      <c r="I35" s="7"/>
+      <c r="J35" s="7"/>
+      <c r="K35" s="7"/>
+      <c r="L35" s="7"/>
+      <c r="M35" s="7"/>
+      <c r="N35" s="7"/>
+      <c r="O35" s="7"/>
+      <c r="P35" s="7"/>
+      <c r="Q35" s="7"/>
+      <c r="R35" s="7"/>
+      <c r="S35" s="7"/>
+      <c r="T35" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -7712,10 +7935,10 @@
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="5" t="s">
         <v>33</v>
       </c>
     </row>
@@ -7797,13 +8020,13 @@
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="5" t="s">
         <v>32</v>
       </c>
     </row>
@@ -8028,25 +8251,25 @@
       </c>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="1" t="s">
+      <c r="A33" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D33" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="E33" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="F33" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="G33" s="1" t="s">
+      <c r="G33" s="5" t="s">
         <v>84</v>
       </c>
     </row>
@@ -10027,26 +10250,26 @@
       </c>
     </row>
     <row r="118" spans="1:8">
-      <c r="A118" s="1" t="s">
+      <c r="A118" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B118" s="1" t="s">
+      <c r="B118" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="C118" s="1" t="s">
+      <c r="C118" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="D118" s="1" t="s">
+      <c r="D118" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="E118" s="1" t="s">
+      <c r="E118" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="F118" s="1" t="s">
+      <c r="F118" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="G118" s="1"/>
-      <c r="H118" s="1"/>
+      <c r="G118" s="5"/>
+      <c r="H118" s="5"/>
     </row>
     <row r="119" spans="1:7">
       <c r="A119" t="s">
@@ -11325,22 +11548,22 @@
       </c>
     </row>
     <row r="184" spans="1:6">
-      <c r="A184" s="1" t="s">
+      <c r="A184" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="B184" s="1" t="s">
+      <c r="B184" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="C184" s="1" t="s">
+      <c r="C184" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="D184" s="1" t="s">
+      <c r="D184" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="E184" s="1" t="s">
+      <c r="E184" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="F184" s="1" t="s">
+      <c r="F184" s="5" t="s">
         <v>192</v>
       </c>
     </row>
@@ -11766,17 +11989,17 @@
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="5" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="5" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="1"/>
+      <c r="A4" s="5"/>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
@@ -11787,17 +12010,17 @@
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="5" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="5" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="5" t="s">
         <v>32</v>
       </c>
     </row>
@@ -11810,67 +12033,67 @@
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="B11" s="1"/>
+      <c r="B11" s="5"/>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B12" s="1"/>
+      <c r="B12" s="5"/>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="5" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="5" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="5" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1" t="s">
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="H16" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I16" s="1" t="s">
+      <c r="I16" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="J16" s="1" t="s">
+      <c r="J16" s="5" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1" t="s">
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F17" s="5" t="s">
         <v>237</v>
       </c>
       <c r="G17" t="s">
@@ -11908,7 +12131,7 @@
       </c>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="5" t="s">
         <v>47</v>
       </c>
       <c r="H21" t="s">
@@ -11916,17 +12139,17 @@
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="5" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="5" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="5" t="s">
         <v>190</v>
       </c>
       <c r="G24" t="s">
@@ -11934,7 +12157,7 @@
       </c>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="5" t="s">
         <v>248</v>
       </c>
       <c r="G25" t="s">
@@ -11942,7 +12165,7 @@
       </c>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="5" t="s">
         <v>192</v>
       </c>
       <c r="G26" t="s">
@@ -11965,12 +12188,12 @@
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="1" t="s">
+      <c r="A31" s="5" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="1" t="s">
+      <c r="A32" s="5" t="s">
         <v>221</v>
       </c>
       <c r="C32" t="s">
@@ -11978,22 +12201,22 @@
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="1" t="s">
+      <c r="A33" s="5" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="1" t="s">
+      <c r="A34" s="5" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="1" t="s">
+      <c r="A35" s="5" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="1" t="s">
+      <c r="A36" s="5" t="s">
         <v>192</v>
       </c>
     </row>
@@ -12002,4 +12225,598 @@
   <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr codeName="Sheet4"/>
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="12.875" customWidth="1"/>
+    <col min="3" max="3" width="24.25" customWidth="1"/>
+    <col min="4" max="4" width="46.5" customWidth="1"/>
+    <col min="5" max="5" width="29.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" t="s">
+        <v>258</v>
+      </c>
+      <c r="C2" t="s">
+        <v>259</v>
+      </c>
+      <c r="D2" t="s">
+        <v>260</v>
+      </c>
+      <c r="E2" t="s">
+        <v>261</v>
+      </c>
+      <c r="F2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>263</v>
+      </c>
+      <c r="B3" t="s">
+        <v>258</v>
+      </c>
+      <c r="C3" t="s">
+        <v>264</v>
+      </c>
+      <c r="D3" t="s">
+        <v>260</v>
+      </c>
+      <c r="E3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>266</v>
+      </c>
+      <c r="B4" t="s">
+        <v>258</v>
+      </c>
+      <c r="C4" t="s">
+        <v>267</v>
+      </c>
+      <c r="D4" t="s">
+        <v>260</v>
+      </c>
+      <c r="E4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>268</v>
+      </c>
+      <c r="B5" t="s">
+        <v>269</v>
+      </c>
+      <c r="C5" t="s">
+        <v>270</v>
+      </c>
+      <c r="D5" t="s">
+        <v>260</v>
+      </c>
+      <c r="E5" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="14" spans="7:7">
+      <c r="G14" t="s">
+        <v>272</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr codeName="Sheet5"/>
+  <dimension ref="A1:O30"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="7" max="7" width="14.875" customWidth="1"/>
+    <col min="8" max="8" width="12.625" customWidth="1"/>
+    <col min="10" max="10" width="12.625" customWidth="1"/>
+    <col min="11" max="12" width="14.875" customWidth="1"/>
+    <col min="13" max="13" width="58.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="C1" s="2"/>
+      <c r="G1" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="2"/>
+      <c r="B2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" t="s">
+        <v>276</v>
+      </c>
+      <c r="G3" t="s">
+        <v>277</v>
+      </c>
+      <c r="H3" t="s">
+        <v>278</v>
+      </c>
+      <c r="I3" t="s">
+        <v>277</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" t="s">
+        <v>281</v>
+      </c>
+      <c r="G4" t="s">
+        <v>282</v>
+      </c>
+      <c r="H4" t="s">
+        <v>278</v>
+      </c>
+      <c r="I4" t="s">
+        <v>277</v>
+      </c>
+      <c r="M4" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" t="s">
+        <v>284</v>
+      </c>
+      <c r="I5" t="s">
+        <v>285</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="L5" s="4"/>
+      <c r="M5" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="6" spans="9:13">
+      <c r="I6" t="s">
+        <v>277</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="M6" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="7" spans="7:14">
+      <c r="G7" t="s">
+        <v>47</v>
+      </c>
+      <c r="H7" t="s">
+        <v>278</v>
+      </c>
+      <c r="I7" t="s">
+        <v>285</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="L7" s="4"/>
+      <c r="M7" t="s">
+        <v>280</v>
+      </c>
+      <c r="N7" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="8" spans="7:13">
+      <c r="G8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H8" t="s">
+        <v>278</v>
+      </c>
+      <c r="I8" t="s">
+        <v>277</v>
+      </c>
+      <c r="M8" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="9" spans="9:13">
+      <c r="I9" t="s">
+        <v>292</v>
+      </c>
+      <c r="K9" t="s">
+        <v>293</v>
+      </c>
+      <c r="M9" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="10" spans="9:13">
+      <c r="I10" t="s">
+        <v>123</v>
+      </c>
+      <c r="J10" t="s">
+        <v>279</v>
+      </c>
+      <c r="K10" t="s">
+        <v>293</v>
+      </c>
+      <c r="L10" t="s">
+        <v>295</v>
+      </c>
+      <c r="M10" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="11" spans="7:13">
+      <c r="G11" t="s">
+        <v>180</v>
+      </c>
+      <c r="H11" t="s">
+        <v>278</v>
+      </c>
+      <c r="I11" t="s">
+        <v>277</v>
+      </c>
+      <c r="M11" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="12" spans="9:13">
+      <c r="I12" t="s">
+        <v>292</v>
+      </c>
+      <c r="K12" t="s">
+        <v>293</v>
+      </c>
+      <c r="M12" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="13" spans="9:13">
+      <c r="I13" t="s">
+        <v>123</v>
+      </c>
+      <c r="J13" t="s">
+        <v>279</v>
+      </c>
+      <c r="K13" t="s">
+        <v>297</v>
+      </c>
+      <c r="L13" t="s">
+        <v>295</v>
+      </c>
+      <c r="M13" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="14" spans="7:13">
+      <c r="G14" t="s">
+        <v>299</v>
+      </c>
+      <c r="H14" t="s">
+        <v>278</v>
+      </c>
+      <c r="I14" t="s">
+        <v>277</v>
+      </c>
+      <c r="M14" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="15" spans="8:13">
+      <c r="H15" t="s">
+        <v>277</v>
+      </c>
+      <c r="I15" t="s">
+        <v>292</v>
+      </c>
+      <c r="K15" t="s">
+        <v>293</v>
+      </c>
+      <c r="M15" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="16" spans="8:14">
+      <c r="H16" t="s">
+        <v>277</v>
+      </c>
+      <c r="I16" t="s">
+        <v>123</v>
+      </c>
+      <c r="J16" t="s">
+        <v>279</v>
+      </c>
+      <c r="K16" t="s">
+        <v>297</v>
+      </c>
+      <c r="L16" t="s">
+        <v>295</v>
+      </c>
+      <c r="M16" t="s">
+        <v>300</v>
+      </c>
+      <c r="N16" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="17" spans="8:10">
+      <c r="H17" t="s">
+        <v>277</v>
+      </c>
+      <c r="I17" t="s">
+        <v>301</v>
+      </c>
+      <c r="J17" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="18" spans="9:10">
+      <c r="I18" t="s">
+        <v>303</v>
+      </c>
+      <c r="J18" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="19" spans="9:10">
+      <c r="I19" t="s">
+        <v>303</v>
+      </c>
+      <c r="J19" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="20" spans="9:9">
+      <c r="I20" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="21" spans="7:13">
+      <c r="G21" t="s">
+        <v>306</v>
+      </c>
+      <c r="H21" t="s">
+        <v>278</v>
+      </c>
+      <c r="I21" t="s">
+        <v>277</v>
+      </c>
+      <c r="M21" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="22" spans="8:13">
+      <c r="H22" t="s">
+        <v>277</v>
+      </c>
+      <c r="I22" t="s">
+        <v>292</v>
+      </c>
+      <c r="K22" t="s">
+        <v>293</v>
+      </c>
+      <c r="M22" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="23" spans="8:15">
+      <c r="H23" t="s">
+        <v>277</v>
+      </c>
+      <c r="I23" t="s">
+        <v>225</v>
+      </c>
+      <c r="J23" t="s">
+        <v>279</v>
+      </c>
+      <c r="K23" t="s">
+        <v>297</v>
+      </c>
+      <c r="L23" t="s">
+        <v>295</v>
+      </c>
+      <c r="M23" t="s">
+        <v>307</v>
+      </c>
+      <c r="N23" t="s">
+        <v>290</v>
+      </c>
+      <c r="O23" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="24" spans="7:13">
+      <c r="G24" t="s">
+        <v>309</v>
+      </c>
+      <c r="H24" t="s">
+        <v>278</v>
+      </c>
+      <c r="I24" t="s">
+        <v>277</v>
+      </c>
+      <c r="J24"/>
+      <c r="M24" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="25" spans="8:13">
+      <c r="H25" t="s">
+        <v>277</v>
+      </c>
+      <c r="I25" t="s">
+        <v>292</v>
+      </c>
+      <c r="J25"/>
+      <c r="K25" t="s">
+        <v>293</v>
+      </c>
+      <c r="M25" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="26" spans="8:15">
+      <c r="H26" t="s">
+        <v>277</v>
+      </c>
+      <c r="I26" t="s">
+        <v>225</v>
+      </c>
+      <c r="J26" t="s">
+        <v>279</v>
+      </c>
+      <c r="K26" t="s">
+        <v>297</v>
+      </c>
+      <c r="L26" t="s">
+        <v>295</v>
+      </c>
+      <c r="M26" t="s">
+        <v>307</v>
+      </c>
+      <c r="N26" t="s">
+        <v>290</v>
+      </c>
+      <c r="O26" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="27" spans="8:10">
+      <c r="H27" t="s">
+        <v>225</v>
+      </c>
+      <c r="I27" t="s">
+        <v>303</v>
+      </c>
+      <c r="J27" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="28" spans="9:9">
+      <c r="I28" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="29" spans="7:14">
+      <c r="G29" t="s">
+        <v>310</v>
+      </c>
+      <c r="H29" t="s">
+        <v>278</v>
+      </c>
+      <c r="I29" t="s">
+        <v>94</v>
+      </c>
+      <c r="J29" t="s">
+        <v>279</v>
+      </c>
+      <c r="M29" t="s">
+        <v>280</v>
+      </c>
+      <c r="N29" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="30" spans="9:11">
+      <c r="I30" t="s">
+        <v>311</v>
+      </c>
+      <c r="K30" t="s">
+        <v>293</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="A1:A2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr codeName="Sheet6"/>
+  <dimension ref="A2:C8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="2"/>
+  <cols>
+    <col min="2" max="2" width="19.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>312</v>
+      </c>
+      <c r="C2" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="8" spans="2:2">
+      <c r="B8" t="s">
+        <v>314</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/src/main/resources/other/总结.xlsx
+++ b/src/main/resources/other/总结.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28245" windowHeight="12465" activeTab="5"/>
+    <workbookView windowWidth="28245" windowHeight="12465" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -13,13 +13,14 @@
     <sheet name="前端调后台" sheetId="6" r:id="rId4"/>
     <sheet name="后台返回数据处理" sheetId="7" r:id="rId5"/>
     <sheet name="前转后的数据" sheetId="8" r:id="rId6"/>
+    <sheet name="接口" sheetId="9" r:id="rId7"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1134" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="329">
   <si>
     <t>场景</t>
   </si>
@@ -964,6 +965,48 @@
   </si>
   <si>
     <t>页面输入字段的数据</t>
+  </si>
+  <si>
+    <t>取菜单信息</t>
+  </si>
+  <si>
+    <t>/initPageInfo</t>
+  </si>
+  <si>
+    <t>webMenuService.getMenu("root")</t>
+  </si>
+  <si>
+    <t>/buttonReq/{eventId}</t>
+  </si>
+  <si>
+    <t>context.getBean(eventId)).execute(requestDto)</t>
+  </si>
+  <si>
+    <t>调对应的功能类</t>
+  </si>
+  <si>
+    <t>取菜单功能页面信息</t>
+  </si>
+  <si>
+    <t>/menuReq/{eventId}</t>
+  </si>
+  <si>
+    <t>webElementService.getPageElementsByParentEle(eventInfo.getMenu(), "start_page",null,publicReq);</t>
+  </si>
+  <si>
+    <t>需要将Table数据定义sql中的变量使用事件中的信息替换</t>
+  </si>
+  <si>
+    <t>/webDataReq/{eventId}</t>
+  </si>
+  <si>
+    <t>webElementService.getPageElementsByParentEle(eventInfo.getMenu(), page,parentEle,publicReq)</t>
+  </si>
+  <si>
+    <t>/swDataReq/{eventId}</t>
+  </si>
+  <si>
+    <t>webElementService.getPageElementsByParentEle(eventInfo.getMenu(), nextPage,null,publicReq);</t>
   </si>
 </sst>
 </file>
@@ -972,8 +1015,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="23">
@@ -1006,17 +1049,15 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color theme="0"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1031,14 +1072,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1053,10 +1094,40 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1068,22 +1139,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1097,9 +1163,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1113,38 +1186,8 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1159,7 +1202,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1171,7 +1280,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1183,37 +1352,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1225,121 +1370,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1378,6 +1421,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -1388,6 +1446,26 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1403,21 +1481,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1445,26 +1508,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1473,10 +1516,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1485,142 +1528,139 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -7395,7 +7435,7 @@
       <c r="A7" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>17</v>
       </c>
       <c r="C7" t="s">
@@ -7403,13 +7443,13 @@
       </c>
     </row>
     <row r="8" spans="2:4">
-      <c r="B8" s="6"/>
+      <c r="B8" s="5"/>
       <c r="D8" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="9" spans="2:12">
-      <c r="B9" s="6"/>
+      <c r="B9" s="5"/>
       <c r="D9" t="s">
         <v>20</v>
       </c>
@@ -7421,15 +7461,15 @@
       </c>
     </row>
     <row r="10" spans="2:20">
-      <c r="B10" s="6"/>
+      <c r="B10" s="5"/>
       <c r="D10" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
       <c r="K10" t="s">
         <v>23</v>
       </c>
@@ -7442,458 +7482,458 @@
       <c r="N10" t="s">
         <v>26</v>
       </c>
-      <c r="O10" s="7"/>
-      <c r="P10" s="7"/>
-      <c r="Q10" s="7"/>
-      <c r="R10" s="7"/>
-      <c r="S10" s="7"/>
-      <c r="T10" s="7"/>
+      <c r="O10" s="6"/>
+      <c r="P10" s="6"/>
+      <c r="Q10" s="6"/>
+      <c r="R10" s="6"/>
+      <c r="S10" s="6"/>
+      <c r="T10" s="6"/>
     </row>
     <row r="11" spans="4:20">
       <c r="D11" t="s">
         <v>27</v>
       </c>
-      <c r="F11" s="7"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="8"/>
-      <c r="N11" s="8"/>
-      <c r="O11" s="8"/>
-      <c r="P11" s="8"/>
-      <c r="Q11" s="8"/>
-      <c r="R11" s="8"/>
-      <c r="S11" s="8"/>
-      <c r="T11" s="8"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
+      <c r="O11" s="7"/>
+      <c r="P11" s="7"/>
+      <c r="Q11" s="7"/>
+      <c r="R11" s="7"/>
+      <c r="S11" s="7"/>
+      <c r="T11" s="7"/>
     </row>
     <row r="12" spans="6:20">
-      <c r="F12" s="7"/>
-      <c r="G12" s="9" t="s">
+      <c r="F12" s="6"/>
+      <c r="G12" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="9"/>
-      <c r="O12" s="9"/>
-      <c r="P12" s="9"/>
-      <c r="Q12" s="9"/>
-      <c r="R12" s="9"/>
-      <c r="S12" s="9"/>
-      <c r="T12" s="9"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8"/>
+      <c r="Q12" s="8"/>
+      <c r="R12" s="8"/>
+      <c r="S12" s="8"/>
+      <c r="T12" s="8"/>
     </row>
     <row r="13" spans="2:20">
-      <c r="B13" s="6"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7">
+      <c r="B13" s="5"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6">
         <v>1</v>
       </c>
-      <c r="H13" s="7" t="s">
+      <c r="H13" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
-      <c r="O13" s="7"/>
-      <c r="P13" s="7"/>
-      <c r="Q13" s="7"/>
-      <c r="R13" s="7"/>
-      <c r="S13" s="7"/>
-      <c r="T13" s="7"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="6"/>
+      <c r="P13" s="6"/>
+      <c r="Q13" s="6"/>
+      <c r="R13" s="6"/>
+      <c r="S13" s="6"/>
+      <c r="T13" s="6"/>
     </row>
     <row r="14" spans="2:20">
-      <c r="B14" s="6"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7">
+      <c r="B14" s="5"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6">
         <v>2</v>
       </c>
-      <c r="H14" s="7" t="s">
+      <c r="H14" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7"/>
-      <c r="N14" s="7"/>
-      <c r="O14" s="7"/>
-      <c r="P14" s="7"/>
-      <c r="Q14" s="7"/>
-      <c r="R14" s="7"/>
-      <c r="S14" s="7"/>
-      <c r="T14" s="7"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6"/>
+      <c r="M14" s="6"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="6"/>
+      <c r="P14" s="6"/>
+      <c r="Q14" s="6"/>
+      <c r="R14" s="6"/>
+      <c r="S14" s="6"/>
+      <c r="T14" s="6"/>
     </row>
     <row r="15" spans="6:20">
-      <c r="F15" s="7"/>
-      <c r="G15" s="7">
+      <c r="F15" s="6"/>
+      <c r="G15" s="6">
         <v>3</v>
       </c>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="7"/>
-      <c r="O15" s="7"/>
-      <c r="P15" s="7"/>
-      <c r="Q15" s="7"/>
-      <c r="R15" s="7"/>
-      <c r="S15" s="7"/>
-      <c r="T15" s="7"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="6"/>
+      <c r="P15" s="6"/>
+      <c r="Q15" s="6"/>
+      <c r="R15" s="6"/>
+      <c r="S15" s="6"/>
+      <c r="T15" s="6"/>
     </row>
     <row r="16" spans="6:20">
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
-      <c r="N16" s="7"/>
-      <c r="O16" s="7"/>
-      <c r="P16" s="7"/>
-      <c r="Q16" s="7"/>
-      <c r="R16" s="7"/>
-      <c r="S16" s="7"/>
-      <c r="T16" s="7"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="6"/>
+      <c r="P16" s="6"/>
+      <c r="Q16" s="6"/>
+      <c r="R16" s="6"/>
+      <c r="S16" s="6"/>
+      <c r="T16" s="6"/>
     </row>
     <row r="17" spans="2:20">
-      <c r="B17" s="6"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="7"/>
-      <c r="M17" s="7"/>
-      <c r="N17" s="7"/>
-      <c r="O17" s="7"/>
-      <c r="P17" s="7"/>
-      <c r="Q17" s="7"/>
-      <c r="R17" s="7"/>
-      <c r="S17" s="7"/>
-      <c r="T17" s="7"/>
+      <c r="B17" s="5"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="6"/>
+      <c r="P17" s="6"/>
+      <c r="Q17" s="6"/>
+      <c r="R17" s="6"/>
+      <c r="S17" s="6"/>
+      <c r="T17" s="6"/>
     </row>
     <row r="18" spans="2:20">
-      <c r="B18" s="6"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
-      <c r="M18" s="7"/>
-      <c r="N18" s="7"/>
-      <c r="O18" s="7"/>
-      <c r="P18" s="7"/>
-      <c r="Q18" s="7"/>
-      <c r="R18" s="7"/>
-      <c r="S18" s="7"/>
-      <c r="T18" s="7"/>
+      <c r="B18" s="5"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="6"/>
+      <c r="P18" s="6"/>
+      <c r="Q18" s="6"/>
+      <c r="R18" s="6"/>
+      <c r="S18" s="6"/>
+      <c r="T18" s="6"/>
     </row>
     <row r="19" spans="6:20">
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="7"/>
-      <c r="L19" s="7"/>
-      <c r="M19" s="7"/>
-      <c r="N19" s="7"/>
-      <c r="O19" s="7"/>
-      <c r="P19" s="7"/>
-      <c r="Q19" s="7"/>
-      <c r="R19" s="7"/>
-      <c r="S19" s="7"/>
-      <c r="T19" s="7"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="6"/>
+      <c r="M19" s="6"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="6"/>
+      <c r="P19" s="6"/>
+      <c r="Q19" s="6"/>
+      <c r="R19" s="6"/>
+      <c r="S19" s="6"/>
+      <c r="T19" s="6"/>
     </row>
     <row r="20" spans="6:20">
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="7"/>
-      <c r="M20" s="7"/>
-      <c r="N20" s="7"/>
-      <c r="O20" s="7"/>
-      <c r="P20" s="7"/>
-      <c r="Q20" s="7"/>
-      <c r="R20" s="7"/>
-      <c r="S20" s="7"/>
-      <c r="T20" s="7"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="6"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="6"/>
+      <c r="M20" s="6"/>
+      <c r="N20" s="6"/>
+      <c r="O20" s="6"/>
+      <c r="P20" s="6"/>
+      <c r="Q20" s="6"/>
+      <c r="R20" s="6"/>
+      <c r="S20" s="6"/>
+      <c r="T20" s="6"/>
     </row>
     <row r="21" spans="2:20">
-      <c r="B21" s="6"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="7"/>
-      <c r="L21" s="7"/>
-      <c r="M21" s="7"/>
-      <c r="N21" s="7"/>
-      <c r="O21" s="7"/>
-      <c r="P21" s="7"/>
-      <c r="Q21" s="7"/>
-      <c r="R21" s="7"/>
-      <c r="S21" s="7"/>
-      <c r="T21" s="7"/>
+      <c r="B21" s="5"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="6"/>
+      <c r="K21" s="6"/>
+      <c r="L21" s="6"/>
+      <c r="M21" s="6"/>
+      <c r="N21" s="6"/>
+      <c r="O21" s="6"/>
+      <c r="P21" s="6"/>
+      <c r="Q21" s="6"/>
+      <c r="R21" s="6"/>
+      <c r="S21" s="6"/>
+      <c r="T21" s="6"/>
     </row>
     <row r="22" spans="2:20">
-      <c r="B22" s="6"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
-      <c r="M22" s="7"/>
-      <c r="N22" s="7"/>
-      <c r="O22" s="7"/>
-      <c r="P22" s="7"/>
-      <c r="Q22" s="7"/>
-      <c r="R22" s="7"/>
-      <c r="S22" s="7"/>
-      <c r="T22" s="7"/>
+      <c r="B22" s="5"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
+      <c r="K22" s="6"/>
+      <c r="L22" s="6"/>
+      <c r="M22" s="6"/>
+      <c r="N22" s="6"/>
+      <c r="O22" s="6"/>
+      <c r="P22" s="6"/>
+      <c r="Q22" s="6"/>
+      <c r="R22" s="6"/>
+      <c r="S22" s="6"/>
+      <c r="T22" s="6"/>
     </row>
     <row r="23" spans="6:20">
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7"/>
-      <c r="J23" s="7"/>
-      <c r="K23" s="7"/>
-      <c r="L23" s="7"/>
-      <c r="M23" s="7"/>
-      <c r="N23" s="7"/>
-      <c r="O23" s="7"/>
-      <c r="P23" s="7"/>
-      <c r="Q23" s="7"/>
-      <c r="R23" s="7"/>
-      <c r="S23" s="7"/>
-      <c r="T23" s="10"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="6"/>
+      <c r="K23" s="6"/>
+      <c r="L23" s="6"/>
+      <c r="M23" s="6"/>
+      <c r="N23" s="6"/>
+      <c r="O23" s="6"/>
+      <c r="P23" s="6"/>
+      <c r="Q23" s="6"/>
+      <c r="R23" s="6"/>
+      <c r="S23" s="6"/>
+      <c r="T23" s="9"/>
     </row>
     <row r="24" spans="6:20">
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
-      <c r="L24" s="7"/>
-      <c r="M24" s="7"/>
-      <c r="N24" s="7"/>
-      <c r="O24" s="7"/>
-      <c r="P24" s="7"/>
-      <c r="Q24" s="7"/>
-      <c r="R24" s="7"/>
-      <c r="S24" s="7"/>
-      <c r="T24" s="7"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="6"/>
+      <c r="K24" s="6"/>
+      <c r="L24" s="6"/>
+      <c r="M24" s="6"/>
+      <c r="N24" s="6"/>
+      <c r="O24" s="6"/>
+      <c r="P24" s="6"/>
+      <c r="Q24" s="6"/>
+      <c r="R24" s="6"/>
+      <c r="S24" s="6"/>
+      <c r="T24" s="6"/>
     </row>
     <row r="25" spans="6:20">
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="7"/>
-      <c r="K25" s="7"/>
-      <c r="L25" s="7"/>
-      <c r="M25" s="7"/>
-      <c r="N25" s="7"/>
-      <c r="O25" s="7"/>
-      <c r="P25" s="7"/>
-      <c r="Q25" s="7"/>
-      <c r="R25" s="7"/>
-      <c r="S25" s="7"/>
-      <c r="T25" s="7"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="6"/>
+      <c r="K25" s="6"/>
+      <c r="L25" s="6"/>
+      <c r="M25" s="6"/>
+      <c r="N25" s="6"/>
+      <c r="O25" s="6"/>
+      <c r="P25" s="6"/>
+      <c r="Q25" s="6"/>
+      <c r="R25" s="6"/>
+      <c r="S25" s="6"/>
+      <c r="T25" s="6"/>
     </row>
     <row r="26" spans="6:20">
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="7"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7"/>
-      <c r="L26" s="7"/>
-      <c r="M26" s="7"/>
-      <c r="N26" s="7"/>
-      <c r="O26" s="7"/>
-      <c r="P26" s="7"/>
-      <c r="Q26" s="7"/>
-      <c r="R26" s="7"/>
-      <c r="S26" s="7"/>
-      <c r="T26" s="7"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6"/>
+      <c r="L26" s="6"/>
+      <c r="M26" s="6"/>
+      <c r="N26" s="6"/>
+      <c r="O26" s="6"/>
+      <c r="P26" s="6"/>
+      <c r="Q26" s="6"/>
+      <c r="R26" s="6"/>
+      <c r="S26" s="6"/>
+      <c r="T26" s="6"/>
     </row>
     <row r="27" spans="6:20">
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
-      <c r="I27" s="7"/>
-      <c r="J27" s="7"/>
-      <c r="K27" s="7"/>
-      <c r="L27" s="7"/>
-      <c r="M27" s="7"/>
-      <c r="N27" s="7"/>
-      <c r="O27" s="7"/>
-      <c r="P27" s="7"/>
-      <c r="Q27" s="7"/>
-      <c r="R27" s="7"/>
-      <c r="S27" s="7"/>
-      <c r="T27" s="7"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="6"/>
+      <c r="J27" s="6"/>
+      <c r="K27" s="6"/>
+      <c r="L27" s="6"/>
+      <c r="M27" s="6"/>
+      <c r="N27" s="6"/>
+      <c r="O27" s="6"/>
+      <c r="P27" s="6"/>
+      <c r="Q27" s="6"/>
+      <c r="R27" s="6"/>
+      <c r="S27" s="6"/>
+      <c r="T27" s="6"/>
     </row>
     <row r="28" spans="6:20">
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
-      <c r="I28" s="7"/>
-      <c r="J28" s="7"/>
-      <c r="K28" s="7"/>
-      <c r="L28" s="7"/>
-      <c r="M28" s="7"/>
-      <c r="N28" s="7"/>
-      <c r="O28" s="7"/>
-      <c r="P28" s="7"/>
-      <c r="Q28" s="7"/>
-      <c r="R28" s="7"/>
-      <c r="S28" s="7"/>
-      <c r="T28" s="7"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
+      <c r="I28" s="6"/>
+      <c r="J28" s="6"/>
+      <c r="K28" s="6"/>
+      <c r="L28" s="6"/>
+      <c r="M28" s="6"/>
+      <c r="N28" s="6"/>
+      <c r="O28" s="6"/>
+      <c r="P28" s="6"/>
+      <c r="Q28" s="6"/>
+      <c r="R28" s="6"/>
+      <c r="S28" s="6"/>
+      <c r="T28" s="6"/>
     </row>
     <row r="29" spans="6:20">
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="7"/>
-      <c r="I29" s="7"/>
-      <c r="J29" s="7"/>
-      <c r="K29" s="7"/>
-      <c r="L29" s="7"/>
-      <c r="M29" s="7"/>
-      <c r="N29" s="7"/>
-      <c r="O29" s="7"/>
-      <c r="P29" s="7"/>
-      <c r="Q29" s="7"/>
-      <c r="R29" s="7"/>
-      <c r="S29" s="7"/>
-      <c r="T29" s="7"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
+      <c r="I29" s="6"/>
+      <c r="J29" s="6"/>
+      <c r="K29" s="6"/>
+      <c r="L29" s="6"/>
+      <c r="M29" s="6"/>
+      <c r="N29" s="6"/>
+      <c r="O29" s="6"/>
+      <c r="P29" s="6"/>
+      <c r="Q29" s="6"/>
+      <c r="R29" s="6"/>
+      <c r="S29" s="6"/>
+      <c r="T29" s="6"/>
     </row>
     <row r="30" spans="6:20">
-      <c r="F30" s="7"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="7"/>
-      <c r="I30" s="7"/>
-      <c r="J30" s="7"/>
-      <c r="K30" s="7"/>
-      <c r="L30" s="7"/>
-      <c r="M30" s="7"/>
-      <c r="N30" s="7"/>
-      <c r="O30" s="7"/>
-      <c r="P30" s="7"/>
-      <c r="Q30" s="7"/>
-      <c r="R30" s="7"/>
-      <c r="S30" s="7"/>
-      <c r="T30" s="7"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="6"/>
+      <c r="J30" s="6"/>
+      <c r="K30" s="6"/>
+      <c r="L30" s="6"/>
+      <c r="M30" s="6"/>
+      <c r="N30" s="6"/>
+      <c r="O30" s="6"/>
+      <c r="P30" s="6"/>
+      <c r="Q30" s="6"/>
+      <c r="R30" s="6"/>
+      <c r="S30" s="6"/>
+      <c r="T30" s="6"/>
     </row>
     <row r="31" spans="6:20">
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
-      <c r="I31" s="7"/>
-      <c r="J31" s="7"/>
-      <c r="K31" s="7"/>
-      <c r="L31" s="7"/>
-      <c r="M31" s="7"/>
-      <c r="N31" s="7"/>
-      <c r="O31" s="7"/>
-      <c r="P31" s="7"/>
-      <c r="Q31" s="7"/>
-      <c r="R31" s="7"/>
-      <c r="S31" s="7"/>
-      <c r="T31" s="7"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="6"/>
+      <c r="J31" s="6"/>
+      <c r="K31" s="6"/>
+      <c r="L31" s="6"/>
+      <c r="M31" s="6"/>
+      <c r="N31" s="6"/>
+      <c r="O31" s="6"/>
+      <c r="P31" s="6"/>
+      <c r="Q31" s="6"/>
+      <c r="R31" s="6"/>
+      <c r="S31" s="6"/>
+      <c r="T31" s="6"/>
     </row>
     <row r="32" spans="6:20">
-      <c r="F32" s="7"/>
-      <c r="G32" s="7"/>
-      <c r="H32" s="7"/>
-      <c r="I32" s="7"/>
-      <c r="J32" s="7"/>
-      <c r="K32" s="7"/>
-      <c r="L32" s="7"/>
-      <c r="M32" s="7"/>
-      <c r="N32" s="7"/>
-      <c r="O32" s="7"/>
-      <c r="P32" s="7"/>
-      <c r="Q32" s="7"/>
-      <c r="R32" s="7"/>
-      <c r="S32" s="7"/>
-      <c r="T32" s="7"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="6"/>
+      <c r="J32" s="6"/>
+      <c r="K32" s="6"/>
+      <c r="L32" s="6"/>
+      <c r="M32" s="6"/>
+      <c r="N32" s="6"/>
+      <c r="O32" s="6"/>
+      <c r="P32" s="6"/>
+      <c r="Q32" s="6"/>
+      <c r="R32" s="6"/>
+      <c r="S32" s="6"/>
+      <c r="T32" s="6"/>
     </row>
     <row r="33" spans="6:20">
-      <c r="F33" s="7"/>
-      <c r="G33" s="7"/>
-      <c r="H33" s="7"/>
-      <c r="I33" s="7"/>
-      <c r="J33" s="7"/>
-      <c r="K33" s="7"/>
-      <c r="L33" s="7"/>
-      <c r="M33" s="7"/>
-      <c r="N33" s="7"/>
-      <c r="O33" s="7"/>
-      <c r="P33" s="7"/>
-      <c r="Q33" s="7"/>
-      <c r="R33" s="7"/>
-      <c r="S33" s="7"/>
-      <c r="T33" s="7"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="6"/>
+      <c r="J33" s="6"/>
+      <c r="K33" s="6"/>
+      <c r="L33" s="6"/>
+      <c r="M33" s="6"/>
+      <c r="N33" s="6"/>
+      <c r="O33" s="6"/>
+      <c r="P33" s="6"/>
+      <c r="Q33" s="6"/>
+      <c r="R33" s="6"/>
+      <c r="S33" s="6"/>
+      <c r="T33" s="6"/>
     </row>
     <row r="34" spans="6:20">
-      <c r="F34" s="7"/>
-      <c r="G34" s="7"/>
-      <c r="H34" s="7"/>
-      <c r="I34" s="7"/>
-      <c r="J34" s="7"/>
-      <c r="K34" s="7"/>
-      <c r="L34" s="7"/>
-      <c r="M34" s="7"/>
-      <c r="N34" s="7"/>
-      <c r="O34" s="7"/>
-      <c r="P34" s="7"/>
-      <c r="Q34" s="7"/>
-      <c r="R34" s="7"/>
-      <c r="S34" s="7"/>
-      <c r="T34" s="7"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="6"/>
+      <c r="J34" s="6"/>
+      <c r="K34" s="6"/>
+      <c r="L34" s="6"/>
+      <c r="M34" s="6"/>
+      <c r="N34" s="6"/>
+      <c r="O34" s="6"/>
+      <c r="P34" s="6"/>
+      <c r="Q34" s="6"/>
+      <c r="R34" s="6"/>
+      <c r="S34" s="6"/>
+      <c r="T34" s="6"/>
     </row>
     <row r="35" spans="6:20">
-      <c r="F35" s="7"/>
-      <c r="G35" s="7"/>
-      <c r="H35" s="7"/>
-      <c r="I35" s="7"/>
-      <c r="J35" s="7"/>
-      <c r="K35" s="7"/>
-      <c r="L35" s="7"/>
-      <c r="M35" s="7"/>
-      <c r="N35" s="7"/>
-      <c r="O35" s="7"/>
-      <c r="P35" s="7"/>
-      <c r="Q35" s="7"/>
-      <c r="R35" s="7"/>
-      <c r="S35" s="7"/>
-      <c r="T35" s="7"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="6"/>
+      <c r="I35" s="6"/>
+      <c r="J35" s="6"/>
+      <c r="K35" s="6"/>
+      <c r="L35" s="6"/>
+      <c r="M35" s="6"/>
+      <c r="N35" s="6"/>
+      <c r="O35" s="6"/>
+      <c r="P35" s="6"/>
+      <c r="Q35" s="6"/>
+      <c r="R35" s="6"/>
+      <c r="S35" s="6"/>
+      <c r="T35" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -7935,10 +7975,10 @@
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>33</v>
       </c>
     </row>
@@ -8020,13 +8060,13 @@
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>32</v>
       </c>
     </row>
@@ -8251,25 +8291,25 @@
       </c>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="5" t="s">
+      <c r="A33" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="D33" s="5" t="s">
+      <c r="D33" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="E33" s="5" t="s">
+      <c r="E33" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="F33" s="5" t="s">
+      <c r="F33" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="G33" s="5" t="s">
+      <c r="G33" s="4" t="s">
         <v>84</v>
       </c>
     </row>
@@ -10250,26 +10290,26 @@
       </c>
     </row>
     <row r="118" spans="1:8">
-      <c r="A118" s="5" t="s">
+      <c r="A118" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B118" s="5" t="s">
+      <c r="B118" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="C118" s="5" t="s">
+      <c r="C118" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="D118" s="5" t="s">
+      <c r="D118" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="E118" s="5" t="s">
+      <c r="E118" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="F118" s="5" t="s">
+      <c r="F118" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="G118" s="5"/>
-      <c r="H118" s="5"/>
+      <c r="G118" s="4"/>
+      <c r="H118" s="4"/>
     </row>
     <row r="119" spans="1:7">
       <c r="A119" t="s">
@@ -11548,22 +11588,22 @@
       </c>
     </row>
     <row r="184" spans="1:6">
-      <c r="A184" s="5" t="s">
+      <c r="A184" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="B184" s="5" t="s">
+      <c r="B184" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="C184" s="5" t="s">
+      <c r="C184" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="D184" s="5" t="s">
+      <c r="D184" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="E184" s="5" t="s">
+      <c r="E184" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="F184" s="5" t="s">
+      <c r="F184" s="4" t="s">
         <v>192</v>
       </c>
     </row>
@@ -11989,17 +12029,17 @@
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="5"/>
+      <c r="A4" s="4"/>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
@@ -12010,17 +12050,17 @@
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="4" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="4" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="4" t="s">
         <v>32</v>
       </c>
     </row>
@@ -12033,67 +12073,67 @@
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="B11" s="5"/>
+      <c r="B11" s="4"/>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="B12" s="5"/>
+      <c r="B12" s="4"/>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="4" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="4" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="4" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5" t="s">
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="G16" s="5" t="s">
+      <c r="G16" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="H16" s="5" t="s">
+      <c r="H16" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="I16" s="5" t="s">
+      <c r="I16" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="J16" s="5" t="s">
+      <c r="J16" s="4" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5" t="s">
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="F17" s="4" t="s">
         <v>237</v>
       </c>
       <c r="G17" t="s">
@@ -12131,7 +12171,7 @@
       </c>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="4" t="s">
         <v>47</v>
       </c>
       <c r="H21" t="s">
@@ -12139,17 +12179,17 @@
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="4" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="4" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="4" t="s">
         <v>190</v>
       </c>
       <c r="G24" t="s">
@@ -12157,7 +12197,7 @@
       </c>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="4" t="s">
         <v>248</v>
       </c>
       <c r="G25" t="s">
@@ -12165,7 +12205,7 @@
       </c>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="4" t="s">
         <v>192</v>
       </c>
       <c r="G26" t="s">
@@ -12188,12 +12228,12 @@
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="4" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="4" t="s">
         <v>221</v>
       </c>
       <c r="C32" t="s">
@@ -12201,22 +12241,22 @@
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="5" t="s">
+      <c r="A33" s="4" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="5" t="s">
+      <c r="A34" s="4" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="5" t="s">
+      <c r="A35" s="4" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="5" t="s">
+      <c r="A36" s="4" t="s">
         <v>192</v>
       </c>
     </row>
@@ -12240,19 +12280,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>257</v>
       </c>
     </row>
@@ -12358,17 +12398,17 @@
       <c r="B1" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="C1" s="2"/>
+      <c r="C1" s="1"/>
       <c r="G1" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="2"/>
-      <c r="B2" s="3" t="s">
+      <c r="A2" s="1"/>
+      <c r="B2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>235</v>
       </c>
     </row>
@@ -12385,10 +12425,10 @@
       <c r="I3" t="s">
         <v>277</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="M3" s="3" t="s">
         <v>280</v>
       </c>
     </row>
@@ -12416,10 +12456,10 @@
       <c r="I5" t="s">
         <v>285</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="L5" s="4"/>
+      <c r="L5" s="3"/>
       <c r="M5" t="s">
         <v>287</v>
       </c>
@@ -12428,7 +12468,7 @@
       <c r="I6" t="s">
         <v>277</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="J6" s="3" t="s">
         <v>279</v>
       </c>
       <c r="M6" t="s">
@@ -12445,13 +12485,13 @@
       <c r="I7" t="s">
         <v>285</v>
       </c>
-      <c r="J7" s="4" t="s">
+      <c r="J7" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="K7" s="4" t="s">
+      <c r="K7" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="L7" s="4"/>
+      <c r="L7" s="3"/>
       <c r="M7" t="s">
         <v>280</v>
       </c>
@@ -12690,7 +12730,6 @@
       <c r="I24" t="s">
         <v>277</v>
       </c>
-      <c r="J24"/>
       <c r="M24" t="s">
         <v>291</v>
       </c>
@@ -12702,7 +12741,6 @@
       <c r="I25" t="s">
         <v>292</v>
       </c>
-      <c r="J25"/>
       <c r="K25" t="s">
         <v>293</v>
       </c>
@@ -12819,4 +12857,73 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr codeName="Sheet7"/>
+  <dimension ref="A2:D9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="19.125" customWidth="1"/>
+    <col min="2" max="2" width="23.75" customWidth="1"/>
+    <col min="3" max="3" width="106" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B2" t="s">
+        <v>316</v>
+      </c>
+      <c r="C2" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4">
+      <c r="B5" t="s">
+        <v>318</v>
+      </c>
+      <c r="C5" t="s">
+        <v>319</v>
+      </c>
+      <c r="D5" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>321</v>
+      </c>
+      <c r="B7" t="s">
+        <v>322</v>
+      </c>
+      <c r="C7" t="s">
+        <v>323</v>
+      </c>
+      <c r="D7" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3">
+      <c r="B8" t="s">
+        <v>325</v>
+      </c>
+      <c r="C8" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3">
+      <c r="B9" t="s">
+        <v>327</v>
+      </c>
+      <c r="C9" t="s">
+        <v>328</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>